--- a/LoanOfficer-A/2023/51 Asiqi.xlsx
+++ b/LoanOfficer-A/2023/51 Asiqi.xlsx
@@ -599,7 +599,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>17400</v>
+        <v>21900</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>18600</v>
+        <v>14100</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -875,9 +875,15 @@
       <c r="I3" s="1">
         <v>61</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="3">
+        <v>45569</v>
+      </c>
+      <c r="K3" s="4">
+        <v>300</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
       <c r="M3" s="1">
         <v>91</v>
       </c>
@@ -913,9 +919,15 @@
       <c r="I4" s="1">
         <v>62</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
+      <c r="J4" s="3">
+        <v>45569</v>
+      </c>
+      <c r="K4" s="4">
+        <v>300</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1">
         <v>92</v>
       </c>
@@ -951,9 +963,15 @@
       <c r="I5" s="1">
         <v>63</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="3">
+        <v>45569</v>
+      </c>
+      <c r="K5" s="4">
+        <v>300</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
       <c r="M5" s="1">
         <v>93</v>
       </c>
@@ -989,9 +1007,15 @@
       <c r="I6" s="1">
         <v>64</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
+      <c r="J6" s="3">
+        <v>45571</v>
+      </c>
+      <c r="K6" s="4">
+        <v>300</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
       <c r="M6" s="1">
         <v>94</v>
       </c>
@@ -1027,9 +1051,15 @@
       <c r="I7" s="1">
         <v>65</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1"/>
+      <c r="J7" s="3">
+        <v>45571</v>
+      </c>
+      <c r="K7" s="4">
+        <v>300</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
       <c r="M7" s="1">
         <v>95</v>
       </c>
@@ -1065,9 +1095,15 @@
       <c r="I8" s="1">
         <v>66</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="1"/>
+      <c r="J8" s="3">
+        <v>45571</v>
+      </c>
+      <c r="K8" s="4">
+        <v>300</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
       <c r="M8" s="1">
         <v>96</v>
       </c>
@@ -1103,9 +1139,15 @@
       <c r="I9" s="1">
         <v>67</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="1"/>
+      <c r="J9" s="3">
+        <v>45571</v>
+      </c>
+      <c r="K9" s="4">
+        <v>300</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
       <c r="M9" s="1">
         <v>97</v>
       </c>
@@ -1141,9 +1183,15 @@
       <c r="I10" s="1">
         <v>68</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="1"/>
+      <c r="J10" s="3">
+        <v>45571</v>
+      </c>
+      <c r="K10" s="4">
+        <v>300</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
       <c r="M10" s="1">
         <v>98</v>
       </c>
@@ -1179,9 +1227,15 @@
       <c r="I11" s="1">
         <v>69</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="1"/>
+      <c r="J11" s="3">
+        <v>45581</v>
+      </c>
+      <c r="K11" s="4">
+        <v>300</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
       <c r="M11" s="1">
         <v>99</v>
       </c>
@@ -1217,9 +1271,15 @@
       <c r="I12" s="1">
         <v>70</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="1"/>
+      <c r="J12" s="3">
+        <v>45581</v>
+      </c>
+      <c r="K12" s="4">
+        <v>300</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
       <c r="M12" s="1">
         <v>100</v>
       </c>
@@ -1255,9 +1315,15 @@
       <c r="I13" s="1">
         <v>71</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="1"/>
+      <c r="J13" s="3">
+        <v>45581</v>
+      </c>
+      <c r="K13" s="4">
+        <v>300</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
       <c r="M13" s="1">
         <v>101</v>
       </c>
@@ -1293,9 +1359,15 @@
       <c r="I14" s="1">
         <v>72</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="1"/>
+      <c r="J14" s="3">
+        <v>45581</v>
+      </c>
+      <c r="K14" s="4">
+        <v>300</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
       <c r="M14" s="1">
         <v>102</v>
       </c>
@@ -1331,9 +1403,15 @@
       <c r="I15" s="1">
         <v>73</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="1"/>
+      <c r="J15" s="3">
+        <v>45581</v>
+      </c>
+      <c r="K15" s="4">
+        <v>300</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
       <c r="M15" s="1">
         <v>103</v>
       </c>
@@ -1927,9 +2005,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>45569</v>
+      </c>
+      <c r="G31" s="4">
+        <v>300</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>
@@ -1959,9 +2043,15 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>45569</v>
+      </c>
+      <c r="G32" s="4">
+        <v>300</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>

--- a/LoanOfficer-A/2023/51 Asiqi.xlsx
+++ b/LoanOfficer-A/2023/51 Asiqi.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>21900</v>
+        <v>28800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>14100</v>
+        <v>7200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -887,9 +887,15 @@
       <c r="M3" s="1">
         <v>91</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="1"/>
+      <c r="N3" s="3">
+        <v>45602</v>
+      </c>
+      <c r="O3" s="4">
+        <v>300</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -931,9 +937,15 @@
       <c r="M4" s="1">
         <v>92</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="1"/>
+      <c r="N4" s="3">
+        <v>45602</v>
+      </c>
+      <c r="O4" s="4">
+        <v>300</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -975,9 +987,15 @@
       <c r="M5" s="1">
         <v>93</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="1"/>
+      <c r="N5" s="3">
+        <v>45602</v>
+      </c>
+      <c r="O5" s="4">
+        <v>300</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1019,9 +1037,15 @@
       <c r="M6" s="1">
         <v>94</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="1"/>
+      <c r="N6" s="3">
+        <v>45602</v>
+      </c>
+      <c r="O6" s="4">
+        <v>300</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1063,9 +1087,15 @@
       <c r="M7" s="1">
         <v>95</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="1"/>
+      <c r="N7" s="3">
+        <v>45602</v>
+      </c>
+      <c r="O7" s="4">
+        <v>300</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1107,9 +1137,15 @@
       <c r="M8" s="1">
         <v>96</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="1"/>
+      <c r="N8" s="3">
+        <v>45602</v>
+      </c>
+      <c r="O8" s="4">
+        <v>300</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1447,9 +1483,15 @@
       <c r="I16" s="1">
         <v>74</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="1"/>
+      <c r="J16" s="3">
+        <v>45588</v>
+      </c>
+      <c r="K16" s="4">
+        <v>300</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
       <c r="M16" s="1">
         <v>104</v>
       </c>
@@ -1485,9 +1527,15 @@
       <c r="I17" s="1">
         <v>75</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="1"/>
+      <c r="J17" s="3">
+        <v>45588</v>
+      </c>
+      <c r="K17" s="4">
+        <v>300</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
       <c r="M17" s="1">
         <v>105</v>
       </c>
@@ -1523,9 +1571,15 @@
       <c r="I18" s="1">
         <v>76</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="1"/>
+      <c r="J18" s="3">
+        <v>45588</v>
+      </c>
+      <c r="K18" s="4">
+        <v>300</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
       <c r="M18" s="1">
         <v>106</v>
       </c>
@@ -1561,9 +1615,15 @@
       <c r="I19" s="1">
         <v>77</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="3">
+        <v>45593</v>
+      </c>
+      <c r="K19" s="4">
+        <v>300</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
       <c r="M19" s="1">
         <v>107</v>
       </c>
@@ -1599,9 +1659,15 @@
       <c r="I20" s="1">
         <v>78</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="1"/>
+      <c r="J20" s="3">
+        <v>45593</v>
+      </c>
+      <c r="K20" s="4">
+        <v>300</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
       <c r="M20" s="1">
         <v>108</v>
       </c>
@@ -1637,9 +1703,15 @@
       <c r="I21" s="1">
         <v>79</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="1"/>
+      <c r="J21" s="3">
+        <v>45593</v>
+      </c>
+      <c r="K21" s="4">
+        <v>300</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
       <c r="M21" s="1">
         <v>109</v>
       </c>
@@ -1675,9 +1747,15 @@
       <c r="I22" s="1">
         <v>80</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="1"/>
+      <c r="J22" s="3">
+        <v>45593</v>
+      </c>
+      <c r="K22" s="4">
+        <v>300</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
       <c r="M22" s="1">
         <v>110</v>
       </c>
@@ -1713,9 +1791,15 @@
       <c r="I23" s="1">
         <v>81</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="1"/>
+      <c r="J23" s="3">
+        <v>45593</v>
+      </c>
+      <c r="K23" s="4">
+        <v>300</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
       <c r="M23" s="1">
         <v>111</v>
       </c>
@@ -1751,9 +1835,15 @@
       <c r="I24" s="1">
         <v>82</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="1"/>
+      <c r="J24" s="3">
+        <v>45596</v>
+      </c>
+      <c r="K24" s="4">
+        <v>300</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
       <c r="M24" s="1">
         <v>112</v>
       </c>
@@ -1789,9 +1879,15 @@
       <c r="I25" s="1">
         <v>83</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="1"/>
+      <c r="J25" s="3">
+        <v>45596</v>
+      </c>
+      <c r="K25" s="4">
+        <v>300</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
       <c r="M25" s="1">
         <v>113</v>
       </c>
@@ -1827,9 +1923,15 @@
       <c r="I26" s="1">
         <v>84</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="1"/>
+      <c r="J26" s="3">
+        <v>45601</v>
+      </c>
+      <c r="K26" s="4">
+        <v>300</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
       <c r="M26" s="1">
         <v>114</v>
       </c>
@@ -1865,9 +1967,15 @@
       <c r="I27" s="1">
         <v>85</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="1"/>
+      <c r="J27" s="3">
+        <v>45601</v>
+      </c>
+      <c r="K27" s="4">
+        <v>300</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
       <c r="M27" s="1">
         <v>115</v>
       </c>
@@ -1903,9 +2011,15 @@
       <c r="I28" s="1">
         <v>86</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="1"/>
+      <c r="J28" s="3">
+        <v>45601</v>
+      </c>
+      <c r="K28" s="4">
+        <v>300</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
       <c r="M28" s="1">
         <v>116</v>
       </c>
@@ -1941,9 +2055,15 @@
       <c r="I29" s="1">
         <v>87</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="1"/>
+      <c r="J29" s="3">
+        <v>45601</v>
+      </c>
+      <c r="K29" s="4">
+        <v>300</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
       <c r="M29" s="1">
         <v>117</v>
       </c>
@@ -1979,9 +2099,15 @@
       <c r="I30" s="1">
         <v>88</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="1"/>
+      <c r="J30" s="3">
+        <v>45601</v>
+      </c>
+      <c r="K30" s="4">
+        <v>300</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
       <c r="M30" s="1">
         <v>118</v>
       </c>
@@ -2017,9 +2143,15 @@
       <c r="I31" s="1">
         <v>89</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="1"/>
+      <c r="J31" s="3">
+        <v>45602</v>
+      </c>
+      <c r="K31" s="4">
+        <v>300</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
       <c r="M31" s="1">
         <v>119</v>
       </c>
@@ -2055,9 +2187,15 @@
       <c r="I32" s="1">
         <v>90</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="1"/>
+      <c r="J32" s="3">
+        <v>45602</v>
+      </c>
+      <c r="K32" s="4">
+        <v>300</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
       <c r="M32" s="1">
         <v>120</v>
       </c>
